--- a/smt-backend/SMT_DATA/CAPACITOR.xlsx
+++ b/smt-backend/SMT_DATA/CAPACITOR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
   <si>
     <t>Reel ID</t>
   </si>
@@ -110,6 +110,24 @@
   </si>
   <si>
     <t>2026-08-20 07:11:53</t>
+  </si>
+  <si>
+    <t>REEL00013</t>
+  </si>
+  <si>
+    <t>PSA4K7S</t>
+  </si>
+  <si>
+    <t>2026-08-25 08:10:55</t>
+  </si>
+  <si>
+    <t>REEL00014</t>
+  </si>
+  <si>
+    <t>PSMH62R</t>
+  </si>
+  <si>
+    <t>2026-08-25 08:37:13</t>
   </si>
 </sst>
 </file>
@@ -574,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -761,6 +779,64 @@
         <v>32</v>
       </c>
     </row>
+    <row r="7" ht="22" customHeight="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="10">
+        <v>5000</v>
+      </c>
+      <c r="F7" s="10">
+        <v>5000</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="6">
+        <v>5000</v>
+      </c>
+      <c r="F8" s="6">
+        <v>5000</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
